--- a/data_lake/datos_diarios_preliminares/dt=2026-10-13/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-10-13/temperaturamed.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{128919AC-B091-4EDE-A230-DB88264D43C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EDE307-7E5A-4883-A535-A2EF057CFCFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Temperatura" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$T$1:$V$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6353,8 +6354,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="191" width="32.42578125" style="50" customWidth="1"/>
-    <col min="192" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="192" width="32.42578125" style="50" customWidth="1"/>
+    <col min="193" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6670,7 +6671,9 @@
       <c r="U5" s="56">
         <v>29.9</v>
       </c>
-      <c r="V5" s="56"/>
+      <c r="V5" s="56">
+        <v>29.5</v>
+      </c>
       <c r="W5" s="56"/>
       <c r="X5" s="56"/>
       <c r="Y5" s="56"/>
@@ -6692,7 +6695,7 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ5" s="71" t="str">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
@@ -6771,7 +6774,9 @@
       <c r="U6" s="56">
         <v>29.6</v>
       </c>
-      <c r="V6" s="56"/>
+      <c r="V6" s="56">
+        <v>29.5</v>
+      </c>
       <c r="W6" s="56"/>
       <c r="X6" s="56"/>
       <c r="Y6" s="56"/>
@@ -6793,7 +6798,7 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ6" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6872,7 +6877,9 @@
       <c r="U7" s="56">
         <v>31.4</v>
       </c>
-      <c r="V7" s="56"/>
+      <c r="V7" s="56">
+        <v>29.3</v>
+      </c>
       <c r="W7" s="56"/>
       <c r="X7" s="56"/>
       <c r="Y7" s="56"/>
@@ -6894,7 +6901,7 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6973,7 +6980,9 @@
       <c r="U8" s="56">
         <v>30.5</v>
       </c>
-      <c r="V8" s="56"/>
+      <c r="V8" s="56">
+        <v>30.5</v>
+      </c>
       <c r="W8" s="56"/>
       <c r="X8" s="56"/>
       <c r="Y8" s="56"/>
@@ -6995,7 +7004,7 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ8" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7074,7 +7083,9 @@
       <c r="U9" s="56">
         <v>30.7</v>
       </c>
-      <c r="V9" s="56"/>
+      <c r="V9" s="56">
+        <v>27.4</v>
+      </c>
       <c r="W9" s="56"/>
       <c r="X9" s="56"/>
       <c r="Y9" s="56"/>
@@ -7096,7 +7107,7 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ9" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7276,7 +7287,9 @@
       <c r="U11" s="56">
         <v>30</v>
       </c>
-      <c r="V11" s="56"/>
+      <c r="V11" s="56">
+        <v>27.1</v>
+      </c>
       <c r="W11" s="56"/>
       <c r="X11" s="56"/>
       <c r="Y11" s="56"/>
@@ -7298,7 +7311,7 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ11" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7375,7 +7388,9 @@
       <c r="U12" s="56">
         <v>29.5</v>
       </c>
-      <c r="V12" s="56"/>
+      <c r="V12" s="56">
+        <v>29.6</v>
+      </c>
       <c r="W12" s="56"/>
       <c r="X12" s="56"/>
       <c r="Y12" s="56"/>
@@ -7397,7 +7412,7 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ12" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7476,7 +7491,9 @@
       <c r="U13" s="56">
         <v>30.1</v>
       </c>
-      <c r="V13" s="56"/>
+      <c r="V13" s="56">
+        <v>25.2</v>
+      </c>
       <c r="W13" s="56"/>
       <c r="X13" s="56"/>
       <c r="Y13" s="56"/>
@@ -7498,7 +7515,7 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ13" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7577,7 +7594,9 @@
       <c r="U14" s="56">
         <v>24.3</v>
       </c>
-      <c r="V14" s="56"/>
+      <c r="V14" s="56">
+        <v>20.5</v>
+      </c>
       <c r="W14" s="56"/>
       <c r="X14" s="56"/>
       <c r="Y14" s="56"/>
@@ -7599,7 +7618,7 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ14" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7678,7 +7697,9 @@
       <c r="U15" s="56">
         <v>30</v>
       </c>
-      <c r="V15" s="56"/>
+      <c r="V15" s="56">
+        <v>28.6</v>
+      </c>
       <c r="W15" s="56"/>
       <c r="X15" s="56"/>
       <c r="Y15" s="56"/>
@@ -7700,7 +7721,7 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ15" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7779,7 +7800,9 @@
       <c r="U16" s="56">
         <v>27.6</v>
       </c>
-      <c r="V16" s="56"/>
+      <c r="V16" s="56">
+        <v>25.4</v>
+      </c>
       <c r="W16" s="56"/>
       <c r="X16" s="56"/>
       <c r="Y16" s="56"/>
@@ -7801,7 +7824,7 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ16" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7880,7 +7903,9 @@
       <c r="U17" s="56">
         <v>24</v>
       </c>
-      <c r="V17" s="56"/>
+      <c r="V17" s="56">
+        <v>19</v>
+      </c>
       <c r="W17" s="56"/>
       <c r="X17" s="56"/>
       <c r="Y17" s="56"/>
@@ -7902,7 +7927,7 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7981,7 +8006,9 @@
       <c r="U18" s="56">
         <v>18.8</v>
       </c>
-      <c r="V18" s="56"/>
+      <c r="V18" s="56">
+        <v>16</v>
+      </c>
       <c r="W18" s="56"/>
       <c r="X18" s="56"/>
       <c r="Y18" s="56"/>
@@ -8003,7 +8030,7 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ18" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8082,7 +8109,9 @@
       <c r="U19" s="56">
         <v>23.3</v>
       </c>
-      <c r="V19" s="56"/>
+      <c r="V19" s="56">
+        <v>21</v>
+      </c>
       <c r="W19" s="56"/>
       <c r="X19" s="56"/>
       <c r="Y19" s="56"/>
@@ -8104,7 +8133,7 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ19" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8183,7 +8212,9 @@
       <c r="U20" s="56">
         <v>22.8</v>
       </c>
-      <c r="V20" s="56"/>
+      <c r="V20" s="56">
+        <v>21.1</v>
+      </c>
       <c r="W20" s="56"/>
       <c r="X20" s="56"/>
       <c r="Y20" s="56"/>
@@ -8205,7 +8236,7 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ20" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8284,7 +8315,9 @@
       <c r="U21" s="56">
         <v>26.1</v>
       </c>
-      <c r="V21" s="56"/>
+      <c r="V21" s="56">
+        <v>22.9</v>
+      </c>
       <c r="W21" s="56"/>
       <c r="X21" s="56"/>
       <c r="Y21" s="56"/>
@@ -8306,7 +8339,7 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ21" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8385,7 +8418,9 @@
       <c r="U22" s="56">
         <v>16.5</v>
       </c>
-      <c r="V22" s="56"/>
+      <c r="V22" s="56">
+        <v>14</v>
+      </c>
       <c r="W22" s="56"/>
       <c r="X22" s="56"/>
       <c r="Y22" s="56"/>
@@ -8407,7 +8442,7 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ22" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8486,7 +8521,9 @@
       <c r="U23" s="56">
         <v>24.2</v>
       </c>
-      <c r="V23" s="56"/>
+      <c r="V23" s="56">
+        <v>22.6</v>
+      </c>
       <c r="W23" s="56"/>
       <c r="X23" s="56"/>
       <c r="Y23" s="56"/>
@@ -8508,7 +8545,7 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ23" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8587,7 +8624,9 @@
       <c r="U24" s="56">
         <v>29.1</v>
       </c>
-      <c r="V24" s="56"/>
+      <c r="V24" s="56">
+        <v>28.7</v>
+      </c>
       <c r="W24" s="56"/>
       <c r="X24" s="56"/>
       <c r="Y24" s="56"/>
@@ -8609,7 +8648,7 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ24" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8688,7 +8727,9 @@
       <c r="U25" s="56">
         <v>19.5</v>
       </c>
-      <c r="V25" s="56"/>
+      <c r="V25" s="56">
+        <v>18.2</v>
+      </c>
       <c r="W25" s="56"/>
       <c r="X25" s="56"/>
       <c r="Y25" s="56"/>
@@ -8710,7 +8751,7 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ25" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8789,7 +8830,9 @@
       <c r="U26" s="56">
         <v>11.8</v>
       </c>
-      <c r="V26" s="56"/>
+      <c r="V26" s="56">
+        <v>11.3</v>
+      </c>
       <c r="W26" s="56"/>
       <c r="X26" s="56"/>
       <c r="Y26" s="56"/>
@@ -8811,7 +8854,7 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ26" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8890,7 +8933,9 @@
       <c r="U27" s="56">
         <v>26.8</v>
       </c>
-      <c r="V27" s="56"/>
+      <c r="V27" s="56">
+        <v>25.5</v>
+      </c>
       <c r="W27" s="56"/>
       <c r="X27" s="56"/>
       <c r="Y27" s="56"/>
@@ -8912,7 +8957,7 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ27" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8991,7 +9036,9 @@
       <c r="U28" s="56">
         <v>25.7</v>
       </c>
-      <c r="V28" s="56"/>
+      <c r="V28" s="56">
+        <v>28.9</v>
+      </c>
       <c r="W28" s="56"/>
       <c r="X28" s="56"/>
       <c r="Y28" s="56"/>
@@ -9013,7 +9060,7 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ28" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9092,7 +9139,9 @@
       <c r="U29" s="56">
         <v>28.7</v>
       </c>
-      <c r="V29" s="56"/>
+      <c r="V29" s="56">
+        <v>29</v>
+      </c>
       <c r="W29" s="56"/>
       <c r="X29" s="56"/>
       <c r="Y29" s="56"/>
@@ -9114,7 +9163,7 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ29" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9193,7 +9242,9 @@
       <c r="U30" s="56">
         <v>26.6</v>
       </c>
-      <c r="V30" s="56"/>
+      <c r="V30" s="56">
+        <v>25.9</v>
+      </c>
       <c r="W30" s="56"/>
       <c r="X30" s="56"/>
       <c r="Y30" s="56"/>
@@ -9215,7 +9266,7 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ30" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9294,7 +9345,9 @@
       <c r="U31" s="98">
         <v>29.2</v>
       </c>
-      <c r="V31" s="98"/>
+      <c r="V31" s="98">
+        <v>28.6</v>
+      </c>
       <c r="W31" s="98"/>
       <c r="X31" s="98"/>
       <c r="Y31" s="98"/>
@@ -9316,7 +9369,7 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ31" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9395,7 +9448,9 @@
       <c r="U32" s="56">
         <v>20.06666666666667</v>
       </c>
-      <c r="V32" s="56"/>
+      <c r="V32" s="56">
+        <v>19.86666666666666</v>
+      </c>
       <c r="W32" s="56"/>
       <c r="X32" s="56"/>
       <c r="Y32" s="56"/>
@@ -9417,7 +9472,7 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ32" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9496,7 +9551,9 @@
       <c r="U33" s="56">
         <v>26.95</v>
       </c>
-      <c r="V33" s="56"/>
+      <c r="V33" s="56">
+        <v>25.4</v>
+      </c>
       <c r="W33" s="56"/>
       <c r="X33" s="56"/>
       <c r="Y33" s="56"/>
@@ -9518,7 +9575,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9597,7 +9654,9 @@
       <c r="U34" s="56">
         <v>21.2</v>
       </c>
-      <c r="V34" s="56"/>
+      <c r="V34" s="56">
+        <v>19.533333333333331</v>
+      </c>
       <c r="W34" s="56"/>
       <c r="X34" s="56"/>
       <c r="Y34" s="56"/>
@@ -9619,7 +9678,7 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ34" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9698,7 +9757,9 @@
       <c r="U35" s="56">
         <v>25.35</v>
       </c>
-      <c r="V35" s="56"/>
+      <c r="V35" s="56">
+        <v>24.15</v>
+      </c>
       <c r="W35" s="56"/>
       <c r="X35" s="56"/>
       <c r="Y35" s="56"/>
@@ -9720,7 +9781,7 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ35" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9799,7 +9860,9 @@
       <c r="U36" s="56">
         <v>19.95</v>
       </c>
-      <c r="V36" s="56"/>
+      <c r="V36" s="56">
+        <v>17.25</v>
+      </c>
       <c r="W36" s="56"/>
       <c r="X36" s="56"/>
       <c r="Y36" s="56"/>
@@ -9821,7 +9884,7 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ36" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9900,7 +9963,9 @@
       <c r="U37" s="56">
         <v>26.8</v>
       </c>
-      <c r="V37" s="56"/>
+      <c r="V37" s="56">
+        <v>24.85</v>
+      </c>
       <c r="W37" s="56"/>
       <c r="X37" s="56"/>
       <c r="Y37" s="56"/>
@@ -9922,7 +9987,7 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ37" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10001,7 +10066,9 @@
       <c r="U38" s="56">
         <v>14.45</v>
       </c>
-      <c r="V38" s="56"/>
+      <c r="V38" s="56">
+        <v>13.85</v>
+      </c>
       <c r="W38" s="56"/>
       <c r="X38" s="56"/>
       <c r="Y38" s="56"/>
@@ -10023,7 +10090,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10102,7 +10169,9 @@
       <c r="U39" s="56">
         <v>21.2</v>
       </c>
-      <c r="V39" s="56"/>
+      <c r="V39" s="56">
+        <v>18.733333333333331</v>
+      </c>
       <c r="W39" s="56"/>
       <c r="X39" s="56"/>
       <c r="Y39" s="56"/>
@@ -10124,7 +10193,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10294,7 +10363,9 @@
       <c r="U41" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="V41" s="56"/>
+      <c r="V41" s="56">
+        <v>17.399999999999999</v>
+      </c>
       <c r="W41" s="56"/>
       <c r="X41" s="56"/>
       <c r="Y41" s="56"/>
@@ -10316,7 +10387,7 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ41" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10393,7 +10464,9 @@
       <c r="U42" s="56">
         <v>29.1</v>
       </c>
-      <c r="V42" s="56"/>
+      <c r="V42" s="56">
+        <v>27.75</v>
+      </c>
       <c r="W42" s="56"/>
       <c r="X42" s="56"/>
       <c r="Y42" s="56"/>
@@ -10415,7 +10488,7 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ42" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10491,8 +10564,12 @@
       <c r="T43" s="56">
         <v>29.55</v>
       </c>
-      <c r="U43" s="56"/>
-      <c r="V43" s="56"/>
+      <c r="U43" s="56">
+        <v>30.15</v>
+      </c>
+      <c r="V43" s="56">
+        <v>28.6</v>
+      </c>
       <c r="W43" s="56"/>
       <c r="X43" s="56"/>
       <c r="Y43" s="56"/>
@@ -10514,7 +10591,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10593,7 +10670,9 @@
       <c r="U44" s="56">
         <v>29</v>
       </c>
-      <c r="V44" s="56"/>
+      <c r="V44" s="56">
+        <v>28.3</v>
+      </c>
       <c r="W44" s="56"/>
       <c r="X44" s="56"/>
       <c r="Y44" s="56"/>
@@ -10615,7 +10694,7 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ44" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10694,7 +10773,9 @@
       <c r="U45" s="56">
         <v>29.1</v>
       </c>
-      <c r="V45" s="56"/>
+      <c r="V45" s="56">
+        <v>27.9</v>
+      </c>
       <c r="W45" s="56"/>
       <c r="X45" s="56"/>
       <c r="Y45" s="56"/>
@@ -10716,7 +10797,7 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ45" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11113,7 +11194,9 @@
       <c r="U50" s="56">
         <v>29.05</v>
       </c>
-      <c r="V50" s="56"/>
+      <c r="V50" s="56">
+        <v>27.6</v>
+      </c>
       <c r="W50" s="56"/>
       <c r="X50" s="56"/>
       <c r="Y50" s="56"/>
@@ -11135,7 +11218,7 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ50" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11372,7 +11455,9 @@
       <c r="U53" s="56">
         <v>27.65</v>
       </c>
-      <c r="V53" s="56"/>
+      <c r="V53" s="56">
+        <v>26.4</v>
+      </c>
       <c r="W53" s="56"/>
       <c r="X53" s="56"/>
       <c r="Y53" s="56"/>
@@ -11394,7 +11479,7 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11473,7 +11558,9 @@
       <c r="U54" s="56">
         <v>30.05</v>
       </c>
-      <c r="V54" s="56"/>
+      <c r="V54" s="56">
+        <v>27.5</v>
+      </c>
       <c r="W54" s="56"/>
       <c r="X54" s="56"/>
       <c r="Y54" s="56"/>
@@ -11495,7 +11582,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11568,7 +11655,9 @@
       <c r="U55" s="56">
         <v>29.15</v>
       </c>
-      <c r="V55" s="56"/>
+      <c r="V55" s="56">
+        <v>27.2</v>
+      </c>
       <c r="W55" s="56"/>
       <c r="X55" s="56"/>
       <c r="Y55" s="56"/>
@@ -11590,7 +11679,7 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ55" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11906,7 +11995,9 @@
       <c r="U59" s="56">
         <v>28.55</v>
       </c>
-      <c r="V59" s="56"/>
+      <c r="V59" s="56">
+        <v>29.1</v>
+      </c>
       <c r="W59" s="56"/>
       <c r="X59" s="56"/>
       <c r="Y59" s="56"/>
@@ -11928,7 +12019,7 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ59" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11994,10 +12085,18 @@
       <c r="R60" s="56">
         <v>26</v>
       </c>
-      <c r="S60" s="56"/>
-      <c r="T60" s="56"/>
-      <c r="U60" s="56"/>
-      <c r="V60" s="56"/>
+      <c r="S60" s="56">
+        <v>25.9</v>
+      </c>
+      <c r="T60" s="56">
+        <v>25.6</v>
+      </c>
+      <c r="U60" s="56">
+        <v>25.7</v>
+      </c>
+      <c r="V60" s="56">
+        <v>25.95</v>
+      </c>
       <c r="W60" s="56"/>
       <c r="X60" s="56"/>
       <c r="Y60" s="56"/>
@@ -12019,7 +12118,7 @@
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ60" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12094,7 +12193,9 @@
       </c>
       <c r="T61" s="56"/>
       <c r="U61" s="56"/>
-      <c r="V61" s="56"/>
+      <c r="V61" s="56">
+        <v>27.7</v>
+      </c>
       <c r="W61" s="56"/>
       <c r="X61" s="56"/>
       <c r="Y61" s="56"/>
@@ -12116,7 +12217,7 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ61" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12195,7 +12296,9 @@
       <c r="U62" s="56">
         <v>27.933333333333341</v>
       </c>
-      <c r="V62" s="56"/>
+      <c r="V62" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="W62" s="56"/>
       <c r="X62" s="56"/>
       <c r="Y62" s="56"/>
@@ -12217,7 +12320,7 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ62" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12454,7 +12557,9 @@
       <c r="U65" s="56">
         <v>26.1</v>
       </c>
-      <c r="V65" s="56"/>
+      <c r="V65" s="56">
+        <v>26.15</v>
+      </c>
       <c r="W65" s="56"/>
       <c r="X65" s="56"/>
       <c r="Y65" s="56"/>
@@ -12476,7 +12581,7 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ65" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12555,7 +12660,9 @@
       <c r="U66" s="56">
         <v>27.95</v>
       </c>
-      <c r="V66" s="56"/>
+      <c r="V66" s="56">
+        <v>26.7</v>
+      </c>
       <c r="W66" s="56"/>
       <c r="X66" s="56"/>
       <c r="Y66" s="56"/>
@@ -12577,7 +12684,7 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ66" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12753,7 +12860,9 @@
       <c r="U68" s="56">
         <v>26.7</v>
       </c>
-      <c r="V68" s="56"/>
+      <c r="V68" s="56">
+        <v>25.1</v>
+      </c>
       <c r="W68" s="56"/>
       <c r="X68" s="56"/>
       <c r="Y68" s="56"/>
@@ -12775,7 +12884,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12854,7 +12963,9 @@
       <c r="U69" s="56">
         <v>26.9</v>
       </c>
-      <c r="V69" s="56"/>
+      <c r="V69" s="56">
+        <v>25.225000000000001</v>
+      </c>
       <c r="W69" s="56"/>
       <c r="X69" s="56"/>
       <c r="Y69" s="56"/>
@@ -12876,7 +12987,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -12949,9 +13060,15 @@
       <c r="S70" s="56">
         <v>27.6</v>
       </c>
-      <c r="T70" s="56"/>
-      <c r="U70" s="56"/>
-      <c r="V70" s="56"/>
+      <c r="T70" s="56">
+        <v>26.266666666666669</v>
+      </c>
+      <c r="U70" s="56">
+        <v>27.466666666666669</v>
+      </c>
+      <c r="V70" s="56">
+        <v>25.86666666666666</v>
+      </c>
       <c r="W70" s="56"/>
       <c r="X70" s="56"/>
       <c r="Y70" s="56"/>
@@ -12973,7 +13090,7 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ70" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13052,7 +13169,9 @@
       <c r="U71" s="56">
         <v>27.63333333333334</v>
       </c>
-      <c r="V71" s="56"/>
+      <c r="V71" s="56">
+        <v>27.466666666666669</v>
+      </c>
       <c r="W71" s="56"/>
       <c r="X71" s="56"/>
       <c r="Y71" s="56"/>
@@ -13074,7 +13193,7 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ71" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13153,7 +13272,9 @@
       <c r="U72" s="56">
         <v>25.833333333333329</v>
       </c>
-      <c r="V72" s="56"/>
+      <c r="V72" s="56">
+        <v>26.833333333333329</v>
+      </c>
       <c r="W72" s="56"/>
       <c r="X72" s="56"/>
       <c r="Y72" s="56"/>
@@ -13175,7 +13296,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13337,9 +13458,11 @@
         <v>22.8</v>
       </c>
       <c r="U74" s="56">
-        <v>22.4</v>
-      </c>
-      <c r="V74" s="56"/>
+        <v>22.35</v>
+      </c>
+      <c r="V74" s="56">
+        <v>22.35</v>
+      </c>
       <c r="W74" s="56"/>
       <c r="X74" s="56"/>
       <c r="Y74" s="56"/>
@@ -13361,7 +13484,7 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ74" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13440,7 +13563,9 @@
       <c r="U75" s="56">
         <v>16.399999999999999</v>
       </c>
-      <c r="V75" s="56"/>
+      <c r="V75" s="56">
+        <v>15.4</v>
+      </c>
       <c r="W75" s="56"/>
       <c r="X75" s="56"/>
       <c r="Y75" s="56"/>
@@ -13462,7 +13587,7 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ75" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13541,7 +13666,9 @@
       <c r="U76" s="56">
         <v>21.65</v>
       </c>
-      <c r="V76" s="56"/>
+      <c r="V76" s="56">
+        <v>21.1</v>
+      </c>
       <c r="W76" s="56"/>
       <c r="X76" s="56"/>
       <c r="Y76" s="56"/>
@@ -13563,7 +13690,7 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ76" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13642,7 +13769,9 @@
       <c r="U77" s="56">
         <v>25.86666666666666</v>
       </c>
-      <c r="V77" s="56"/>
+      <c r="V77" s="56">
+        <v>24.733333333333331</v>
+      </c>
       <c r="W77" s="56"/>
       <c r="X77" s="56"/>
       <c r="Y77" s="56"/>
@@ -13664,7 +13793,7 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ77" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13741,7 +13870,9 @@
       <c r="U78" s="56">
         <v>31.15</v>
       </c>
-      <c r="V78" s="56"/>
+      <c r="V78" s="56">
+        <v>27.35</v>
+      </c>
       <c r="W78" s="56"/>
       <c r="X78" s="56"/>
       <c r="Y78" s="56"/>
@@ -13763,7 +13894,7 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ78" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13842,7 +13973,9 @@
       <c r="U79" s="56">
         <v>32.200000000000003</v>
       </c>
-      <c r="V79" s="56"/>
+      <c r="V79" s="56">
+        <v>30.2</v>
+      </c>
       <c r="W79" s="56"/>
       <c r="X79" s="56"/>
       <c r="Y79" s="56"/>
@@ -13864,7 +13997,7 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ79" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13943,7 +14076,9 @@
       <c r="U80" s="56">
         <v>22.86666666666666</v>
       </c>
-      <c r="V80" s="56"/>
+      <c r="V80" s="56">
+        <v>20.866666666666671</v>
+      </c>
       <c r="W80" s="56"/>
       <c r="X80" s="56"/>
       <c r="Y80" s="56"/>
@@ -13965,7 +14100,7 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ80" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14038,7 +14173,9 @@
         <v>25.4</v>
       </c>
       <c r="U81" s="56"/>
-      <c r="V81" s="56"/>
+      <c r="V81" s="56">
+        <v>25.8</v>
+      </c>
       <c r="W81" s="56"/>
       <c r="X81" s="56"/>
       <c r="Y81" s="56"/>
@@ -14060,7 +14197,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14137,7 +14274,9 @@
       <c r="U82" s="56">
         <v>27.6</v>
       </c>
-      <c r="V82" s="56"/>
+      <c r="V82" s="56">
+        <v>27.166666666666671</v>
+      </c>
       <c r="W82" s="56"/>
       <c r="X82" s="56"/>
       <c r="Y82" s="56"/>
@@ -14159,7 +14298,7 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ82" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14392,7 +14531,9 @@
       <c r="U85" s="56">
         <v>31.75</v>
       </c>
-      <c r="V85" s="56"/>
+      <c r="V85" s="56">
+        <v>30.5</v>
+      </c>
       <c r="W85" s="56"/>
       <c r="X85" s="56"/>
       <c r="Y85" s="56"/>
@@ -14414,7 +14555,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14586,7 +14727,9 @@
       <c r="U87" s="56">
         <v>30.9</v>
       </c>
-      <c r="V87" s="56"/>
+      <c r="V87" s="56">
+        <v>28</v>
+      </c>
       <c r="W87" s="56"/>
       <c r="X87" s="56"/>
       <c r="Y87" s="56"/>
@@ -14608,7 +14751,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14687,7 +14830,9 @@
       <c r="U88" s="56">
         <v>28.25</v>
       </c>
-      <c r="V88" s="56"/>
+      <c r="V88" s="56">
+        <v>26.6</v>
+      </c>
       <c r="W88" s="56"/>
       <c r="X88" s="56"/>
       <c r="Y88" s="56"/>
@@ -14709,7 +14854,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14786,7 +14931,9 @@
         <v>30.45</v>
       </c>
       <c r="U89" s="56"/>
-      <c r="V89" s="56"/>
+      <c r="V89" s="56">
+        <v>27.95</v>
+      </c>
       <c r="W89" s="56"/>
       <c r="X89" s="56"/>
       <c r="Y89" s="56"/>
@@ -14808,7 +14955,7 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ89" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14881,7 +15028,9 @@
       <c r="U90" s="56">
         <v>30.85</v>
       </c>
-      <c r="V90" s="56"/>
+      <c r="V90" s="56">
+        <v>28.95</v>
+      </c>
       <c r="W90" s="56"/>
       <c r="X90" s="56"/>
       <c r="Y90" s="56"/>
@@ -14903,7 +15052,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14980,7 +15129,9 @@
       <c r="U91" s="56">
         <v>27.45</v>
       </c>
-      <c r="V91" s="56"/>
+      <c r="V91" s="56">
+        <v>28.85</v>
+      </c>
       <c r="W91" s="56"/>
       <c r="X91" s="56"/>
       <c r="Y91" s="56"/>
@@ -15002,7 +15153,7 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ91" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15081,7 +15232,9 @@
       <c r="U92" s="56">
         <v>17.75</v>
       </c>
-      <c r="V92" s="56"/>
+      <c r="V92" s="56">
+        <v>16.05</v>
+      </c>
       <c r="W92" s="56"/>
       <c r="X92" s="56"/>
       <c r="Y92" s="56"/>
@@ -15103,7 +15256,7 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ92" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15182,7 +15335,9 @@
       <c r="U93" s="56">
         <v>23.733333333333331</v>
       </c>
-      <c r="V93" s="56"/>
+      <c r="V93" s="56">
+        <v>22.666666666666671</v>
+      </c>
       <c r="W93" s="56"/>
       <c r="X93" s="56"/>
       <c r="Y93" s="56"/>
@@ -15204,7 +15359,7 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ93" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15283,7 +15438,9 @@
       <c r="U94" s="56">
         <v>17.45</v>
       </c>
-      <c r="V94" s="56"/>
+      <c r="V94" s="56">
+        <v>16</v>
+      </c>
       <c r="W94" s="56"/>
       <c r="X94" s="56"/>
       <c r="Y94" s="56"/>
@@ -15305,7 +15462,7 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ94" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15384,7 +15541,9 @@
       <c r="U95" s="56">
         <v>16</v>
       </c>
-      <c r="V95" s="56"/>
+      <c r="V95" s="56">
+        <v>15.3</v>
+      </c>
       <c r="W95" s="56"/>
       <c r="X95" s="56"/>
       <c r="Y95" s="56"/>
@@ -15406,7 +15565,7 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ95" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15564,7 +15723,9 @@
       <c r="U97" s="56">
         <v>16.5</v>
       </c>
-      <c r="V97" s="56"/>
+      <c r="V97" s="56">
+        <v>16.350000000000001</v>
+      </c>
       <c r="W97" s="56"/>
       <c r="X97" s="56"/>
       <c r="Y97" s="56"/>
@@ -15586,7 +15747,7 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ97" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15665,7 +15826,9 @@
       <c r="U98" s="56">
         <v>13.9</v>
       </c>
-      <c r="V98" s="56"/>
+      <c r="V98" s="56">
+        <v>13.65</v>
+      </c>
       <c r="W98" s="56"/>
       <c r="X98" s="56"/>
       <c r="Y98" s="56"/>
@@ -15687,7 +15850,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15766,7 +15929,9 @@
       <c r="U99" s="56">
         <v>14.8</v>
       </c>
-      <c r="V99" s="56"/>
+      <c r="V99" s="56">
+        <v>12.866666666666671</v>
+      </c>
       <c r="W99" s="56"/>
       <c r="X99" s="56"/>
       <c r="Y99" s="56"/>
@@ -15788,7 +15953,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15960,7 +16125,9 @@
       <c r="U101" s="56">
         <v>14.3</v>
       </c>
-      <c r="V101" s="56"/>
+      <c r="V101" s="56">
+        <v>13.65</v>
+      </c>
       <c r="W101" s="56"/>
       <c r="X101" s="56"/>
       <c r="Y101" s="56"/>
@@ -15982,7 +16149,7 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ101" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16314,7 +16481,9 @@
       <c r="U105" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="V105" s="56"/>
+      <c r="V105" s="56">
+        <v>17</v>
+      </c>
       <c r="W105" s="56"/>
       <c r="X105" s="56"/>
       <c r="Y105" s="56"/>
@@ -16336,7 +16505,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16413,7 +16582,9 @@
       <c r="U106" s="56">
         <v>15.1</v>
       </c>
-      <c r="V106" s="56"/>
+      <c r="V106" s="56">
+        <v>14.5</v>
+      </c>
       <c r="W106" s="56"/>
       <c r="X106" s="56"/>
       <c r="Y106" s="56"/>
@@ -16435,7 +16606,7 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ106" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16593,7 +16764,9 @@
       <c r="U108" s="56">
         <v>16.350000000000001</v>
       </c>
-      <c r="V108" s="56"/>
+      <c r="V108" s="56">
+        <v>14.25</v>
+      </c>
       <c r="W108" s="56"/>
       <c r="X108" s="56"/>
       <c r="Y108" s="56"/>
@@ -16615,7 +16788,7 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ108" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16694,7 +16867,9 @@
       <c r="U109" s="56">
         <v>16.25</v>
       </c>
-      <c r="V109" s="56"/>
+      <c r="V109" s="56">
+        <v>13.95</v>
+      </c>
       <c r="W109" s="56"/>
       <c r="X109" s="56"/>
       <c r="Y109" s="56"/>
@@ -16716,7 +16891,7 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ109" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16795,7 +16970,9 @@
       <c r="U110" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="V110" s="56"/>
+      <c r="V110" s="56">
+        <v>17.06666666666667</v>
+      </c>
       <c r="W110" s="56"/>
       <c r="X110" s="56"/>
       <c r="Y110" s="56"/>
@@ -16817,7 +16994,7 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ110" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16896,7 +17073,9 @@
       <c r="U111" s="56">
         <v>16.399999999999999</v>
       </c>
-      <c r="V111" s="56"/>
+      <c r="V111" s="56">
+        <v>15.2</v>
+      </c>
       <c r="W111" s="56"/>
       <c r="X111" s="56"/>
       <c r="Y111" s="56"/>
@@ -16918,7 +17097,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16997,7 +17176,9 @@
       <c r="U112" s="56">
         <v>19.866666666666671</v>
       </c>
-      <c r="V112" s="56"/>
+      <c r="V112" s="56">
+        <v>18.2</v>
+      </c>
       <c r="W112" s="56"/>
       <c r="X112" s="56"/>
       <c r="Y112" s="56"/>
@@ -17019,7 +17200,7 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ112" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17096,7 +17277,9 @@
       <c r="U113" s="56">
         <v>20.8</v>
       </c>
-      <c r="V113" s="56"/>
+      <c r="V113" s="56">
+        <v>18.06666666666667</v>
+      </c>
       <c r="W113" s="56"/>
       <c r="X113" s="56"/>
       <c r="Y113" s="56"/>
@@ -17118,7 +17301,7 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ113" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17288,7 +17471,9 @@
       <c r="U115" s="56">
         <v>27.4</v>
       </c>
-      <c r="V115" s="56"/>
+      <c r="V115" s="56">
+        <v>26.8</v>
+      </c>
       <c r="W115" s="56"/>
       <c r="X115" s="56"/>
       <c r="Y115" s="56"/>
@@ -17310,7 +17495,7 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ115" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17389,7 +17574,9 @@
       <c r="U116" s="56">
         <v>19.666666666666671</v>
       </c>
-      <c r="V116" s="56"/>
+      <c r="V116" s="56">
+        <v>19.466666666666669</v>
+      </c>
       <c r="W116" s="56"/>
       <c r="X116" s="56"/>
       <c r="Y116" s="56"/>
@@ -17411,7 +17598,7 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ116" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17587,7 +17774,9 @@
       <c r="U118" s="56">
         <v>30.333333333333329</v>
       </c>
-      <c r="V118" s="56"/>
+      <c r="V118" s="56">
+        <v>30</v>
+      </c>
       <c r="W118" s="56"/>
       <c r="X118" s="56"/>
       <c r="Y118" s="56"/>
@@ -17609,7 +17798,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17953,7 +18142,9 @@
       <c r="U122" s="56">
         <v>12</v>
       </c>
-      <c r="V122" s="56"/>
+      <c r="V122" s="56">
+        <v>13</v>
+      </c>
       <c r="W122" s="56"/>
       <c r="X122" s="56"/>
       <c r="Y122" s="56"/>
@@ -17975,7 +18166,7 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ122" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18133,7 +18324,9 @@
       <c r="U124" s="56">
         <v>18</v>
       </c>
-      <c r="V124" s="56"/>
+      <c r="V124" s="56">
+        <v>18.333333333333329</v>
+      </c>
       <c r="W124" s="56"/>
       <c r="X124" s="56"/>
       <c r="Y124" s="56"/>
@@ -18155,7 +18348,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18307,7 +18500,9 @@
         <v>12.93333333333333</v>
       </c>
       <c r="U126" s="56"/>
-      <c r="V126" s="56"/>
+      <c r="V126" s="56">
+        <v>12.733333333333331</v>
+      </c>
       <c r="W126" s="56"/>
       <c r="X126" s="56"/>
       <c r="Y126" s="56"/>
@@ -18329,7 +18524,7 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ126" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18645,7 +18840,9 @@
       <c r="U130" s="56">
         <v>15.03333333333333</v>
       </c>
-      <c r="V130" s="56"/>
+      <c r="V130" s="56">
+        <v>13.53333333333333</v>
+      </c>
       <c r="W130" s="56"/>
       <c r="X130" s="56"/>
       <c r="Y130" s="56"/>
@@ -18667,7 +18864,7 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ130" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18746,7 +18943,9 @@
       <c r="U131" s="56">
         <v>18.2</v>
       </c>
-      <c r="V131" s="56"/>
+      <c r="V131" s="56">
+        <v>15.65</v>
+      </c>
       <c r="W131" s="56"/>
       <c r="X131" s="56"/>
       <c r="Y131" s="56"/>
@@ -18768,7 +18967,7 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ131" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18926,7 +19125,9 @@
       <c r="U133" s="56">
         <v>14.7</v>
       </c>
-      <c r="V133" s="56"/>
+      <c r="V133" s="56">
+        <v>13.66666666666667</v>
+      </c>
       <c r="W133" s="56"/>
       <c r="X133" s="56"/>
       <c r="Y133" s="56"/>
@@ -18948,7 +19149,7 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ133" s="71" t="str">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
@@ -19027,7 +19228,9 @@
       <c r="U134" s="56">
         <v>18.733333333333331</v>
       </c>
-      <c r="V134" s="56"/>
+      <c r="V134" s="56">
+        <v>16.666666666666661</v>
+      </c>
       <c r="W134" s="56"/>
       <c r="X134" s="56"/>
       <c r="Y134" s="56"/>
@@ -19049,7 +19252,7 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ134" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19126,7 +19329,9 @@
       <c r="U135" s="56">
         <v>16.95</v>
       </c>
-      <c r="V135" s="56"/>
+      <c r="V135" s="56">
+        <v>17.149999999999999</v>
+      </c>
       <c r="W135" s="56"/>
       <c r="X135" s="56"/>
       <c r="Y135" s="56"/>
@@ -19148,7 +19353,7 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ135" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19225,7 +19430,9 @@
       <c r="U136" s="56">
         <v>13.2</v>
       </c>
-      <c r="V136" s="56"/>
+      <c r="V136" s="56">
+        <v>12.866666666666671</v>
+      </c>
       <c r="W136" s="56"/>
       <c r="X136" s="56"/>
       <c r="Y136" s="56"/>
@@ -19247,7 +19454,7 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ136" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19405,7 +19612,9 @@
       <c r="U138" s="56">
         <v>21.133333333333329</v>
       </c>
-      <c r="V138" s="56"/>
+      <c r="V138" s="56">
+        <v>20.466666666666669</v>
+      </c>
       <c r="W138" s="56"/>
       <c r="X138" s="56"/>
       <c r="Y138" s="56"/>
@@ -19427,7 +19636,7 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ138" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19506,7 +19715,9 @@
       <c r="U139" s="56">
         <v>14.725</v>
       </c>
-      <c r="V139" s="56"/>
+      <c r="V139" s="56">
+        <v>13.6</v>
+      </c>
       <c r="W139" s="56"/>
       <c r="X139" s="56"/>
       <c r="Y139" s="56"/>
@@ -19528,7 +19739,7 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ139" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19607,7 +19818,9 @@
       <c r="U140" s="56">
         <v>15.25</v>
       </c>
-      <c r="V140" s="56"/>
+      <c r="V140" s="56">
+        <v>15.65</v>
+      </c>
       <c r="W140" s="56"/>
       <c r="X140" s="56"/>
       <c r="Y140" s="56"/>
@@ -19629,7 +19842,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19708,7 +19921,9 @@
       <c r="U141" s="56">
         <v>14.33333333333333</v>
       </c>
-      <c r="V141" s="56"/>
+      <c r="V141" s="56">
+        <v>13</v>
+      </c>
       <c r="W141" s="56"/>
       <c r="X141" s="56"/>
       <c r="Y141" s="56"/>
@@ -19730,7 +19945,7 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ141" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19809,7 +20024,9 @@
       <c r="U142" s="56">
         <v>12.4</v>
       </c>
-      <c r="V142" s="56"/>
+      <c r="V142" s="56">
+        <v>12.1</v>
+      </c>
       <c r="W142" s="56"/>
       <c r="X142" s="56"/>
       <c r="Y142" s="56"/>
@@ -19831,7 +20048,7 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ142" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19910,7 +20127,9 @@
       <c r="U143" s="56">
         <v>26.8</v>
       </c>
-      <c r="V143" s="56"/>
+      <c r="V143" s="56">
+        <v>27.13333333333334</v>
+      </c>
       <c r="W143" s="56"/>
       <c r="X143" s="56"/>
       <c r="Y143" s="56"/>
@@ -19932,7 +20151,7 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ143" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20011,7 +20230,9 @@
       <c r="U144" s="56">
         <v>17.333333333333329</v>
       </c>
-      <c r="V144" s="56"/>
+      <c r="V144" s="56">
+        <v>15.66666666666667</v>
+      </c>
       <c r="W144" s="56"/>
       <c r="X144" s="56"/>
       <c r="Y144" s="56"/>
@@ -20033,7 +20254,7 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ144" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20112,7 +20333,9 @@
       <c r="U145" s="56">
         <v>22.13333333333334</v>
       </c>
-      <c r="V145" s="56"/>
+      <c r="V145" s="56">
+        <v>19.2</v>
+      </c>
       <c r="W145" s="56"/>
       <c r="X145" s="56"/>
       <c r="Y145" s="56"/>
@@ -20134,7 +20357,7 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ145" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20312,7 +20535,9 @@
       <c r="U147" s="56">
         <v>26.466666666666669</v>
       </c>
-      <c r="V147" s="56"/>
+      <c r="V147" s="56">
+        <v>23.266666666666669</v>
+      </c>
       <c r="W147" s="56"/>
       <c r="X147" s="56"/>
       <c r="Y147" s="56"/>
@@ -20334,7 +20559,7 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ147" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20410,8 +20635,12 @@
       <c r="T148" s="56">
         <v>27.8</v>
       </c>
-      <c r="U148" s="56"/>
-      <c r="V148" s="56"/>
+      <c r="U148" s="56">
+        <v>29.2</v>
+      </c>
+      <c r="V148" s="56">
+        <v>27.466666666666669</v>
+      </c>
       <c r="W148" s="56"/>
       <c r="X148" s="56"/>
       <c r="Y148" s="56"/>
@@ -20433,7 +20662,7 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ148" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20922,8 +21151,12 @@
       <c r="T154" s="56">
         <v>18.899999999999999</v>
       </c>
-      <c r="U154" s="56"/>
-      <c r="V154" s="56"/>
+      <c r="U154" s="56">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="V154" s="56">
+        <v>19.649999999999999</v>
+      </c>
       <c r="W154" s="56"/>
       <c r="X154" s="56"/>
       <c r="Y154" s="56"/>
@@ -20945,7 +21178,7 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ154" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21024,7 +21257,9 @@
       <c r="U155" s="56">
         <v>28.466666666666669</v>
       </c>
-      <c r="V155" s="56"/>
+      <c r="V155" s="56">
+        <v>26.533333333333331</v>
+      </c>
       <c r="W155" s="56"/>
       <c r="X155" s="56"/>
       <c r="Y155" s="56"/>
@@ -21046,7 +21281,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21193,8 +21428,12 @@
       <c r="T157" s="56">
         <v>27.4</v>
       </c>
-      <c r="U157" s="56"/>
-      <c r="V157" s="56"/>
+      <c r="U157" s="56">
+        <v>29.06666666666667</v>
+      </c>
+      <c r="V157" s="56">
+        <v>27.066666666666659</v>
+      </c>
       <c r="W157" s="56"/>
       <c r="X157" s="56"/>
       <c r="Y157" s="56"/>
@@ -21216,7 +21455,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21289,7 +21528,9 @@
       <c r="U158" s="56">
         <v>29.86666666666666</v>
       </c>
-      <c r="V158" s="56"/>
+      <c r="V158" s="56">
+        <v>26.666666666666671</v>
+      </c>
       <c r="W158" s="56"/>
       <c r="X158" s="56"/>
       <c r="Y158" s="56"/>
@@ -21311,7 +21552,7 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ158" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21390,7 +21631,9 @@
       <c r="U159" s="56">
         <v>20.399999999999999</v>
       </c>
-      <c r="V159" s="56"/>
+      <c r="V159" s="56">
+        <v>18.866666666666671</v>
+      </c>
       <c r="W159" s="56"/>
       <c r="X159" s="56"/>
       <c r="Y159" s="56"/>
@@ -21412,7 +21655,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21489,7 +21732,9 @@
         <v>26.533333333333331</v>
       </c>
       <c r="U160" s="56"/>
-      <c r="V160" s="56"/>
+      <c r="V160" s="56">
+        <v>25</v>
+      </c>
       <c r="W160" s="56"/>
       <c r="X160" s="56"/>
       <c r="Y160" s="56"/>
@@ -21511,7 +21756,7 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ160" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21669,7 +21914,9 @@
       <c r="U162" s="56">
         <v>29</v>
       </c>
-      <c r="V162" s="56"/>
+      <c r="V162" s="56">
+        <v>25.866666666666671</v>
+      </c>
       <c r="W162" s="56"/>
       <c r="X162" s="56"/>
       <c r="Y162" s="56"/>
@@ -21691,7 +21938,7 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ162" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21770,7 +22017,9 @@
       <c r="U163" s="56">
         <v>21.93333333333333</v>
       </c>
-      <c r="V163" s="56"/>
+      <c r="V163" s="56">
+        <v>20.733333333333331</v>
+      </c>
       <c r="W163" s="56"/>
       <c r="X163" s="56"/>
       <c r="Y163" s="56"/>
@@ -21792,7 +22041,7 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ163" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21871,7 +22120,9 @@
       <c r="U164" s="56">
         <v>25.1</v>
       </c>
-      <c r="V164" s="56"/>
+      <c r="V164" s="56">
+        <v>24.25</v>
+      </c>
       <c r="W164" s="56"/>
       <c r="X164" s="56"/>
       <c r="Y164" s="56"/>
@@ -21893,7 +22144,7 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ164" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22051,7 +22302,9 @@
       <c r="U166" s="56">
         <v>14.6</v>
       </c>
-      <c r="V166" s="56"/>
+      <c r="V166" s="56">
+        <v>13.2</v>
+      </c>
       <c r="W166" s="56"/>
       <c r="X166" s="56"/>
       <c r="Y166" s="56"/>
@@ -22073,7 +22326,7 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ166" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22152,7 +22405,9 @@
       <c r="U167" s="56">
         <v>21</v>
       </c>
-      <c r="V167" s="56"/>
+      <c r="V167" s="56">
+        <v>18.733333333333331</v>
+      </c>
       <c r="W167" s="56"/>
       <c r="X167" s="56"/>
       <c r="Y167" s="56"/>
@@ -22174,7 +22429,7 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ167" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22253,7 +22508,9 @@
       <c r="U168" s="56">
         <v>28.7</v>
       </c>
-      <c r="V168" s="56"/>
+      <c r="V168" s="56">
+        <v>25</v>
+      </c>
       <c r="W168" s="56"/>
       <c r="X168" s="56"/>
       <c r="Y168" s="56"/>
@@ -22275,7 +22532,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22354,7 +22611,9 @@
       <c r="U169" s="56">
         <v>10.3</v>
       </c>
-      <c r="V169" s="56"/>
+      <c r="V169" s="56">
+        <v>9.1</v>
+      </c>
       <c r="W169" s="56"/>
       <c r="X169" s="56"/>
       <c r="Y169" s="56"/>
@@ -22376,7 +22635,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22649,7 +22908,9 @@
       <c r="U172" s="56">
         <v>25.3</v>
       </c>
-      <c r="V172" s="56"/>
+      <c r="V172" s="56">
+        <v>23.35</v>
+      </c>
       <c r="W172" s="56"/>
       <c r="X172" s="56"/>
       <c r="Y172" s="56"/>
@@ -22671,7 +22932,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22750,7 +23011,9 @@
       <c r="U173" s="56">
         <v>23.75</v>
       </c>
-      <c r="V173" s="56"/>
+      <c r="V173" s="56">
+        <v>22.15</v>
+      </c>
       <c r="W173" s="56"/>
       <c r="X173" s="56"/>
       <c r="Y173" s="56"/>
@@ -22772,7 +23035,7 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ173" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22927,7 +23190,9 @@
       <c r="T175" s="56">
         <v>23</v>
       </c>
-      <c r="U175" s="56"/>
+      <c r="U175" s="56">
+        <v>21.666666666666671</v>
+      </c>
       <c r="V175" s="56"/>
       <c r="W175" s="56"/>
       <c r="X175" s="56"/>
@@ -22950,7 +23215,7 @@
       <c r="AO175" s="56"/>
       <c r="AP175" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ175" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23184,8 +23449,12 @@
       <c r="T178" s="56">
         <v>25.4</v>
       </c>
-      <c r="U178" s="56"/>
-      <c r="V178" s="56"/>
+      <c r="U178" s="56">
+        <v>23.866666666666671</v>
+      </c>
+      <c r="V178" s="56">
+        <v>23.066666666666659</v>
+      </c>
       <c r="W178" s="56"/>
       <c r="X178" s="56"/>
       <c r="Y178" s="56"/>
@@ -23207,7 +23476,7 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ178" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23286,7 +23555,9 @@
       <c r="U179" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="V179" s="56"/>
+      <c r="V179" s="56">
+        <v>16.350000000000001</v>
+      </c>
       <c r="W179" s="56"/>
       <c r="X179" s="56"/>
       <c r="Y179" s="56"/>
@@ -23308,7 +23579,7 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ179" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23721,7 +23992,9 @@
       <c r="U184" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="V184" s="56"/>
+      <c r="V184" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="W184" s="56"/>
       <c r="X184" s="56"/>
       <c r="Y184" s="56"/>
@@ -23743,7 +24016,7 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ184" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23820,7 +24093,9 @@
       <c r="U185" s="56">
         <v>28.2</v>
       </c>
-      <c r="V185" s="56"/>
+      <c r="V185" s="56">
+        <v>26.8</v>
+      </c>
       <c r="W185" s="56"/>
       <c r="X185" s="56"/>
       <c r="Y185" s="56"/>
@@ -23842,7 +24117,7 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ185" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24079,7 +24354,9 @@
       <c r="U188" s="56">
         <v>16.266666666666669</v>
       </c>
-      <c r="V188" s="56"/>
+      <c r="V188" s="56">
+        <v>15.66666666666667</v>
+      </c>
       <c r="W188" s="56"/>
       <c r="X188" s="56"/>
       <c r="Y188" s="56"/>
@@ -24101,7 +24378,7 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ188" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24172,7 +24449,9 @@
       <c r="U189" s="56">
         <v>30</v>
       </c>
-      <c r="V189" s="56"/>
+      <c r="V189" s="56">
+        <v>25.4</v>
+      </c>
       <c r="W189" s="56"/>
       <c r="X189" s="56"/>
       <c r="Y189" s="56"/>
@@ -24194,7 +24473,7 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ189" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24273,7 +24552,9 @@
       <c r="U190" s="56">
         <v>29.066666666666659</v>
       </c>
-      <c r="V190" s="56"/>
+      <c r="V190" s="56">
+        <v>26.13333333333334</v>
+      </c>
       <c r="W190" s="56"/>
       <c r="X190" s="56"/>
       <c r="Y190" s="56"/>
@@ -24295,7 +24576,7 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ190" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24473,7 +24754,9 @@
       <c r="U192" s="56">
         <v>25.86666666666666</v>
       </c>
-      <c r="V192" s="56"/>
+      <c r="V192" s="56">
+        <v>23.533333333333331</v>
+      </c>
       <c r="W192" s="56"/>
       <c r="X192" s="56"/>
       <c r="Y192" s="56"/>
@@ -24495,7 +24778,7 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ192" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24661,7 +24944,9 @@
       <c r="U194" s="56">
         <v>21.666666666666671</v>
       </c>
-      <c r="V194" s="56"/>
+      <c r="V194" s="56">
+        <v>21.8</v>
+      </c>
       <c r="W194" s="56"/>
       <c r="X194" s="56"/>
       <c r="Y194" s="56"/>
@@ -24683,7 +24968,7 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ194" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24960,7 +25245,9 @@
       <c r="U197" s="56">
         <v>25.533333333333331</v>
       </c>
-      <c r="V197" s="56"/>
+      <c r="V197" s="56">
+        <v>22</v>
+      </c>
       <c r="W197" s="56"/>
       <c r="X197" s="56"/>
       <c r="Y197" s="56"/>
@@ -24981,11 +25268,11 @@
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
-        <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>11</v>
+        <f t="shared" ref="AP197:AP212" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
+        <v>12</v>
       </c>
       <c r="AQ197" s="71" t="str">
-        <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
+        <f t="shared" ref="AQ197:AQ212" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
         <v/>
       </c>
       <c r="AR197" s="71">
@@ -24993,7 +25280,7 @@
         <v>24.067391244533901</v>
       </c>
       <c r="AS197" s="71" t="str">
-        <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
+        <f t="shared" ref="AS197:AS212" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
         <v/>
       </c>
     </row>
@@ -25061,7 +25348,9 @@
       <c r="U198" s="56">
         <v>21.95</v>
       </c>
-      <c r="V198" s="56"/>
+      <c r="V198" s="56">
+        <v>20.149999999999999</v>
+      </c>
       <c r="W198" s="56"/>
       <c r="X198" s="56"/>
       <c r="Y198" s="56"/>
@@ -25083,7 +25372,7 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ198" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25162,7 +25451,9 @@
       <c r="U199" s="56">
         <v>15.66666666666667</v>
       </c>
-      <c r="V199" s="56"/>
+      <c r="V199" s="56">
+        <v>16.133333333333329</v>
+      </c>
       <c r="W199" s="56"/>
       <c r="X199" s="56"/>
       <c r="Y199" s="56"/>
@@ -25184,7 +25475,7 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ199" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25261,7 +25552,9 @@
       <c r="U200" s="56">
         <v>15.95</v>
       </c>
-      <c r="V200" s="56"/>
+      <c r="V200" s="56">
+        <v>13.5</v>
+      </c>
       <c r="W200" s="56"/>
       <c r="X200" s="56"/>
       <c r="Y200" s="56"/>
@@ -25283,7 +25576,7 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ200" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25362,7 +25655,9 @@
       <c r="U201" s="56">
         <v>27.4</v>
       </c>
-      <c r="V201" s="56"/>
+      <c r="V201" s="56">
+        <v>24.75</v>
+      </c>
       <c r="W201" s="56"/>
       <c r="X201" s="56"/>
       <c r="Y201" s="56"/>
@@ -25384,7 +25679,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25460,8 +25755,12 @@
       <c r="T202" s="56">
         <v>14.15</v>
       </c>
-      <c r="U202" s="56"/>
-      <c r="V202" s="56"/>
+      <c r="U202" s="56">
+        <v>14.15</v>
+      </c>
+      <c r="V202" s="56">
+        <v>14.25</v>
+      </c>
       <c r="W202" s="56"/>
       <c r="X202" s="56"/>
       <c r="Y202" s="56"/>
@@ -25483,7 +25782,7 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ202" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25562,7 +25861,9 @@
       <c r="U203" s="56">
         <v>14.133333333333329</v>
       </c>
-      <c r="V203" s="56"/>
+      <c r="V203" s="56">
+        <v>14.33333333333333</v>
+      </c>
       <c r="W203" s="56"/>
       <c r="X203" s="56"/>
       <c r="Y203" s="56"/>
@@ -25584,7 +25885,7 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ203" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25838,8 +26139,12 @@
       <c r="T206" s="56">
         <v>15.15</v>
       </c>
-      <c r="U206" s="56"/>
-      <c r="V206" s="56"/>
+      <c r="U206" s="56">
+        <v>14.85</v>
+      </c>
+      <c r="V206" s="56">
+        <v>13.05</v>
+      </c>
       <c r="W206" s="56"/>
       <c r="X206" s="56"/>
       <c r="Y206" s="56"/>
@@ -25861,7 +26166,7 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ206" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25927,7 +26232,9 @@
       <c r="R207" s="56">
         <v>13.93333333333333</v>
       </c>
-      <c r="S207" s="56"/>
+      <c r="S207" s="56">
+        <v>16</v>
+      </c>
       <c r="T207" s="56"/>
       <c r="U207" s="56"/>
       <c r="V207" s="56"/>
@@ -25952,7 +26259,7 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ207" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26029,7 +26336,9 @@
       <c r="U208" s="56">
         <v>15.9</v>
       </c>
-      <c r="V208" s="56"/>
+      <c r="V208" s="56">
+        <v>13.95</v>
+      </c>
       <c r="W208" s="56"/>
       <c r="X208" s="56"/>
       <c r="Y208" s="56"/>
@@ -26051,7 +26360,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26130,7 +26439,9 @@
       <c r="U209" s="56">
         <v>10.55</v>
       </c>
-      <c r="V209" s="56"/>
+      <c r="V209" s="56">
+        <v>10.65</v>
+      </c>
       <c r="W209" s="56"/>
       <c r="X209" s="56"/>
       <c r="Y209" s="56"/>
@@ -26152,7 +26463,7 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ209" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26326,7 +26637,9 @@
       <c r="U211" s="56">
         <v>9.25</v>
       </c>
-      <c r="V211" s="56"/>
+      <c r="V211" s="56">
+        <v>8.5</v>
+      </c>
       <c r="W211" s="56"/>
       <c r="X211" s="56"/>
       <c r="Y211" s="56"/>
@@ -26348,7 +26661,7 @@
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ211" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26423,7 +26736,9 @@
       <c r="U212" s="56">
         <v>29.4</v>
       </c>
-      <c r="V212" s="56"/>
+      <c r="V212" s="56">
+        <v>29</v>
+      </c>
       <c r="W212" s="56"/>
       <c r="X212" s="56"/>
       <c r="Y212" s="56"/>
@@ -26445,7 +26760,7 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ212" s="71" t="str">
         <f t="shared" si="10"/>
